--- a/PCB/bom/Attendance_Management_System_BOM_LCSC.xlsx
+++ b/PCB/bom/Attendance_Management_System_BOM_LCSC.xlsx
@@ -14,7 +14,7 @@
     <sheet name="LCSC_Order" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">BOM!$A$7:$AJ$51</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">BOM!$A$7:$AK$51</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,11 +26,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="357">
   <si>
     <t xml:space="preserve">Two ways to use this BOM</t>
   </si>
   <si>
+    <t xml:space="preserve">Every orderable symbol in the schematic now carries a hidden LCSC field with the number used here, so the Fabrication Toolkit fills the LCSC column of production/bom.csv itself once the board is updated from the schematic.</t>
+  </si>
+  <si>
     <t xml:space="preserve">JLCPCB assembly: upload jlcpcb_bom.csv (next to this workbook, same as the JLCPCB_BOM sheet) with production/positions.csv from the Fabrication Toolkit. U1 is out of stock there, so mark it "do not place" and solder it yourself, or send one to JLCPCB as a consigned part. J2, J3, J4, J7 and TH1 are through-hole: add JLCPCB's through-hole assembly or solder them by hand. Check part rotations in JLCPCB's placement preview before you pay.</t>
   </si>
   <si>
@@ -52,7 +55,7 @@
     <t xml:space="preserve">U1, STM32L432KCU6: out of stock at LCSC and JLCPCB. Digi-Key had 1,307 (497-STM32L432KCU6TRCT-ND) on the same day. The 128 kB STM32L432KBU6, which LCSC does stock, is not a substitute: the firmware stores the attendance log in the upper 128 kB of flash.</t>
   </si>
   <si>
-    <t xml:space="preserve">Y2 + C6/C7: no 4 pF-load 3.2x1.5 mm crystal is stocked, so Y2 is a 6 pF Epson FC-135 and C6/C7 default to the 8.2 pF alternate. Update C6/C7 to 8.2p in the schematic so it matches what you build.</t>
+    <t xml:space="preserve">Y2 + C6/C7: no 4 pF-load 3.2x1.5 mm crystal is stocked, so Y2 is a 6 pF Epson FC-135 and C6/C7 were changed to 8.2 pF in the schematic (2026-09-26).</t>
   </si>
   <si>
     <t xml:space="preserve">R6: 1 kΩ sets a 1 A charge current, above the 500 mA a USB-C sink with 5.1 kΩ CC resistors may draw. The 2 kΩ alternate gives 500 mA.</t>
@@ -187,6 +190,9 @@
     <t xml:space="preserve">Order: JLCPCB library</t>
   </si>
   <si>
+    <t xml:space="preserve">Boards the JLCPCB stock covers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Est. cost (USD)</t>
   </si>
   <si>
@@ -283,34 +289,25 @@
     <t xml:space="preserve">C6,C7</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacitor, C0G 50 V (32.768 kHz load caps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC0805CRNPO9BN4R3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2201928</t>
+    <t xml:space="preserve">8.2p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitor, 8.2 pF 50 V C0G ±0.25 pF (32.768 kHz load caps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0805CG8R2C500NT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1840</t>
   </si>
   <si>
     <t xml:space="preserve">Extended</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0805CG8R2C500NT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALTERNATE ON by default (8.2 pF): Y2 below has CL = 6 pF, so C6/C7 need about 2 x (6 - 2 pF stray) = 8 pF. With 4.3 pF the RTC runs ~70 ppm fast (~6 s/day). Change C6/C7 to 8.2p in the schematic.</t>
+    <t xml:space="preserve">Y2 has CL = 6 pF, so C6/C7 need about 2 x (6 - 2 pF stray) = 8 pF. Changed from 4.3p in the schematic on 2026-09-26.</t>
   </si>
   <si>
     <t xml:space="preserve">C9,C10</t>
@@ -1021,7 +1018,7 @@
     <t xml:space="preserve">C95361</t>
   </si>
   <si>
-    <t xml:space="preserve">Epson FC-135. No 4 pF crystal comes in 3.2x1.5 mm at LCSC (4 pF parts are 2.0x1.2 mm), so C6/C7 go to 8.2 pF.</t>
+    <t xml:space="preserve">Epson FC-135. No 4 pF crystal comes in 3.2x1.5 mm at LCSC (4 pF parts are 2.0x1.2 mm), so C6/C7 are 8.2 pF.</t>
   </si>
   <si>
     <t xml:space="preserve">AE3</t>
@@ -1677,7 +1674,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
@@ -1688,44 +1685,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1734,7 +1731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1745,34 +1742,39 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1791,7 +1793,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AK56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1820,24 +1822,25 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>1</v>
@@ -1845,117 +1848,120 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V7" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W7" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y7" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA7" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB7" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC7" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AD7" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AE7" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AF7" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AG7" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AH7" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AI7" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AJ7" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="AK7" s="7" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1963,37 +1969,37 @@
         <v>1</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>12</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>9771320</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>18198776</v>
+        <v>18198779</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>20</v>
@@ -2002,7 +2008,7 @@
         <v>0.0192</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
@@ -2014,7 +2020,7 @@
       <c r="W8" s="8"/>
       <c r="X8" s="10"/>
       <c r="Y8" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z8" s="11" t="n">
         <v>0</v>
@@ -2047,14 +2053,18 @@
         <f aca="false">IF(O8="Y",T8,J8)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH8" s="12" t="n">
+      <c r="AH8" s="9" t="n">
+        <f aca="false">IF(OR(AF8="",Y8&lt;&gt;"Y"),"",INT(IF(O8="Y",V8,L8)/C8))</f>
+        <v>1516564</v>
+      </c>
+      <c r="AI8" s="12" t="n">
         <f aca="false">AB8*IF(O8="Y",X8,N8)</f>
         <v>0.384</v>
       </c>
-      <c r="AI8" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ8" s="8" t="str">
+      <c r="AJ8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK8" s="8" t="str">
         <f aca="false">IF(AF8="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF8&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -2064,37 +2074,37 @@
         <v>2</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K9" s="14" t="n">
         <v>1968760</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>2946823</v>
+        <v>2946783</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>20</v>
@@ -2103,7 +2113,7 @@
         <v>0.0348</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
@@ -2115,7 +2125,7 @@
       <c r="W9" s="13"/>
       <c r="X9" s="15"/>
       <c r="Y9" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z9" s="11" t="n">
         <v>0</v>
@@ -2148,14 +2158,18 @@
         <f aca="false">IF(O9="Y",T9,J9)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH9" s="16" t="n">
+      <c r="AH9" s="14" t="n">
+        <f aca="false">IF(OR(AF9="",Y9&lt;&gt;"Y"),"",INT(IF(O9="Y",V9,L9)/C9))</f>
+        <v>1473391</v>
+      </c>
+      <c r="AI9" s="16" t="n">
         <f aca="false">AB9*IF(O9="Y",X9,N9)</f>
         <v>0.696</v>
       </c>
-      <c r="AI9" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ9" s="13" t="str">
+      <c r="AJ9" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK9" s="13" t="str">
         <f aca="false">IF(AF9="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF9&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -2165,31 +2179,31 @@
         <v>3</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>1184600</v>
@@ -2204,7 +2218,7 @@
         <v>0.0116</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
@@ -2216,7 +2230,7 @@
       <c r="W10" s="8"/>
       <c r="X10" s="10"/>
       <c r="Y10" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z10" s="11" t="n">
         <v>0</v>
@@ -2249,12 +2263,16 @@
         <f aca="false">IF(O10="Y",T10,J10)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH10" s="12" t="n">
+      <c r="AH10" s="9" t="n">
+        <f aca="false">IF(OR(AF10="",Y10&lt;&gt;"Y"),"",INT(IF(O10="Y",V10,L10)/C10))</f>
+        <v>2362717</v>
+      </c>
+      <c r="AI10" s="12" t="n">
         <f aca="false">AB10*IF(O10="Y",X10,N10)</f>
         <v>0.58</v>
       </c>
-      <c r="AI10" s="8"/>
-      <c r="AJ10" s="8" t="str">
+      <c r="AJ10" s="8"/>
+      <c r="AK10" s="8" t="str">
         <f aca="false">IF(AF10="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF10&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -2264,37 +2282,37 @@
         <v>4</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>271630</v>
+        <v>271530</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>2506788</v>
+        <v>2506668</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>10</v>
@@ -2303,7 +2321,7 @@
         <v>0.0403</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
@@ -2315,7 +2333,7 @@
       <c r="W11" s="13"/>
       <c r="X11" s="15"/>
       <c r="Y11" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z11" s="11" t="n">
         <v>0</v>
@@ -2348,91 +2366,77 @@
         <f aca="false">IF(O11="Y",T11,J11)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH11" s="16" t="n">
+      <c r="AH11" s="14" t="n">
+        <f aca="false">IF(OR(AF11="",Y11&lt;&gt;"Y"),"",INT(IF(O11="Y",V11,L11)/C11))</f>
+        <v>1253334</v>
+      </c>
+      <c r="AI11" s="16" t="n">
         <f aca="false">AB11*IF(O11="Y",X11,N11)</f>
         <v>0.403</v>
       </c>
-      <c r="AI11" s="13"/>
-      <c r="AJ11" s="13" t="str">
+      <c r="AJ11" s="13"/>
+      <c r="AK11" s="13" t="str">
         <f aca="false">IF(AF11="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF11&amp;".html","open"))</f>
         <v>open</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>550</v>
+        <v>34100</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>664</v>
+        <v>34887</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>50</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>0.0166</v>
+        <v>0.011</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="P12" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="T12" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v>34100</v>
-      </c>
-      <c r="V12" s="9" t="n">
-        <v>34887</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="X12" s="10" t="n">
-        <v>0.011</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="10"/>
       <c r="Y12" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z12" s="11" t="n">
         <v>0</v>
@@ -2465,14 +2469,18 @@
         <f aca="false">IF(O12="Y",T12,J12)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH12" s="12" t="n">
+      <c r="AH12" s="9" t="n">
+        <f aca="false">IF(OR(AF12="",Y12&lt;&gt;"Y"),"",INT(IF(O12="Y",V12,L12)/C12))</f>
+        <v>17443</v>
+      </c>
+      <c r="AI12" s="12" t="n">
         <f aca="false">AB12*IF(O12="Y",X12,N12)</f>
         <v>0.55</v>
       </c>
-      <c r="AI12" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="AJ12" s="8" t="str">
+      <c r="AJ12" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK12" s="8" t="str">
         <f aca="false">IF(AF12="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF12&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -2482,31 +2490,31 @@
         <v>6</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="F13" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="13" t="s">
+      <c r="I13" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="J13" s="13" t="s">
         <v>99</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="K13" s="14" t="n">
         <v>118450</v>
@@ -2521,7 +2529,7 @@
         <v>0.0095</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
@@ -2533,7 +2541,7 @@
       <c r="W13" s="13"/>
       <c r="X13" s="15"/>
       <c r="Y13" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z13" s="11" t="n">
         <v>0</v>
@@ -2566,12 +2574,16 @@
         <f aca="false">IF(O13="Y",T13,J13)&amp;""</f>
         <v>Preferred ext.</v>
       </c>
-      <c r="AH13" s="16" t="n">
+      <c r="AH13" s="14" t="n">
+        <f aca="false">IF(OR(AF13="",Y13&lt;&gt;"Y"),"",INT(IF(O13="Y",V13,L13)/C13))</f>
+        <v>82953</v>
+      </c>
+      <c r="AI13" s="16" t="n">
         <f aca="false">AB13*IF(O13="Y",X13,N13)</f>
         <v>0.475</v>
       </c>
-      <c r="AI13" s="13"/>
-      <c r="AJ13" s="13" t="str">
+      <c r="AJ13" s="13"/>
+      <c r="AK13" s="13" t="str">
         <f aca="false">IF(AF13="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF13&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -2581,31 +2593,31 @@
         <v>7</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D14" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H14" s="8" t="s">
+      <c r="I14" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>105</v>
-      </c>
       <c r="J14" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>183200</v>
@@ -2620,7 +2632,7 @@
         <v>0.0081</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -2632,7 +2644,7 @@
       <c r="W14" s="8"/>
       <c r="X14" s="10"/>
       <c r="Y14" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z14" s="11" t="n">
         <v>0</v>
@@ -2665,14 +2677,18 @@
         <f aca="false">IF(O14="Y",T14,J14)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH14" s="12" t="n">
+      <c r="AH14" s="9" t="n">
+        <f aca="false">IF(OR(AF14="",Y14&lt;&gt;"Y"),"",INT(IF(O14="Y",V14,L14)/C14))</f>
+        <v>46166</v>
+      </c>
+      <c r="AI14" s="12" t="n">
         <f aca="false">AB14*IF(O14="Y",X14,N14)</f>
         <v>0.405</v>
       </c>
-      <c r="AI14" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ14" s="8" t="str">
+      <c r="AJ14" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="AK14" s="8" t="str">
         <f aca="false">IF(AF14="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF14&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -2682,31 +2698,31 @@
         <v>8</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="F15" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H15" s="13" t="s">
+      <c r="I15" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>111</v>
-      </c>
       <c r="J15" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K15" s="14" t="n">
         <v>467700</v>
@@ -2721,7 +2737,7 @@
         <v>0.0184</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
@@ -2733,7 +2749,7 @@
       <c r="W15" s="13"/>
       <c r="X15" s="15"/>
       <c r="Y15" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z15" s="11" t="n">
         <v>0</v>
@@ -2766,12 +2782,16 @@
         <f aca="false">IF(O15="Y",T15,J15)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH15" s="16" t="n">
+      <c r="AH15" s="14" t="n">
+        <f aca="false">IF(OR(AF15="",Y15&lt;&gt;"Y"),"",INT(IF(O15="Y",V15,L15)/C15))</f>
+        <v>247269</v>
+      </c>
+      <c r="AI15" s="16" t="n">
         <f aca="false">AB15*IF(O15="Y",X15,N15)</f>
         <v>1.84</v>
       </c>
-      <c r="AI15" s="13"/>
-      <c r="AJ15" s="13" t="str">
+      <c r="AJ15" s="13"/>
+      <c r="AK15" s="13" t="str">
         <f aca="false">IF(AF15="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF15&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -2781,31 +2801,31 @@
         <v>9</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="8" t="s">
+      <c r="I16" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>116</v>
-      </c>
       <c r="J16" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>45050</v>
@@ -2820,7 +2840,7 @@
         <v>0.0101</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
@@ -2832,7 +2852,7 @@
       <c r="W16" s="8"/>
       <c r="X16" s="10"/>
       <c r="Y16" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z16" s="11" t="n">
         <v>0</v>
@@ -2865,14 +2885,18 @@
         <f aca="false">IF(O16="Y",T16,J16)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH16" s="12" t="n">
+      <c r="AH16" s="9" t="n">
+        <f aca="false">IF(OR(AF16="",Y16&lt;&gt;"Y"),"",INT(IF(O16="Y",V16,L16)/C16))</f>
+        <v>23693</v>
+      </c>
+      <c r="AI16" s="12" t="n">
         <f aca="false">AB16*IF(O16="Y",X16,N16)</f>
         <v>0.505</v>
       </c>
-      <c r="AI16" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AJ16" s="8" t="str">
+      <c r="AJ16" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AK16" s="8" t="str">
         <f aca="false">IF(AF16="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF16&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -2882,31 +2906,31 @@
         <v>10</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="F17" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" s="13" t="s">
+      <c r="I17" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>122</v>
-      </c>
       <c r="J17" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K17" s="14" t="n">
         <v>15500</v>
@@ -2921,7 +2945,7 @@
         <v>0.016</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
@@ -2933,7 +2957,7 @@
       <c r="W17" s="13"/>
       <c r="X17" s="15"/>
       <c r="Y17" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z17" s="11" t="n">
         <v>0</v>
@@ -2966,14 +2990,18 @@
         <f aca="false">IF(O17="Y",T17,J17)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH17" s="16" t="n">
+      <c r="AH17" s="14" t="n">
+        <f aca="false">IF(OR(AF17="",Y17&lt;&gt;"Y"),"",INT(IF(O17="Y",V17,L17)/C17))</f>
+        <v>7767</v>
+      </c>
+      <c r="AI17" s="16" t="n">
         <f aca="false">AB17*IF(O17="Y",X17,N17)</f>
         <v>0.8</v>
       </c>
-      <c r="AI17" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ17" s="13" t="str">
+      <c r="AJ17" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AK17" s="13" t="str">
         <f aca="false">IF(AF17="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF17&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -2983,37 +3011,37 @@
         <v>11</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D18" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" s="8" t="s">
+      <c r="I18" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>128</v>
-      </c>
       <c r="J18" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>1512600</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>5574638</v>
+        <v>5574591</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>20</v>
@@ -3022,7 +3050,7 @@
         <v>0.0798</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
@@ -3034,7 +3062,7 @@
       <c r="W18" s="8"/>
       <c r="X18" s="10"/>
       <c r="Y18" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z18" s="11" t="n">
         <v>0</v>
@@ -3067,12 +3095,16 @@
         <f aca="false">IF(O18="Y",T18,J18)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH18" s="12" t="n">
+      <c r="AH18" s="9" t="n">
+        <f aca="false">IF(OR(AF18="",Y18&lt;&gt;"Y"),"",INT(IF(O18="Y",V18,L18)/C18))</f>
+        <v>1858197</v>
+      </c>
+      <c r="AI18" s="12" t="n">
         <f aca="false">AB18*IF(O18="Y",X18,N18)</f>
         <v>1.596</v>
       </c>
-      <c r="AI18" s="8"/>
-      <c r="AJ18" s="8" t="str">
+      <c r="AJ18" s="8"/>
+      <c r="AK18" s="8" t="str">
         <f aca="false">IF(AF18="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF18&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -3082,37 +3114,37 @@
         <v>12</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>4</v>
       </c>
       <c r="D19" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="F19" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="13" t="s">
+      <c r="I19" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="J19" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K19" s="14" t="n">
         <v>194170</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>685839</v>
+        <v>685779</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>10</v>
@@ -3121,7 +3153,7 @@
         <v>0.0536</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
@@ -3133,7 +3165,7 @@
       <c r="W19" s="13"/>
       <c r="X19" s="15"/>
       <c r="Y19" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z19" s="11" t="n">
         <v>0</v>
@@ -3166,12 +3198,16 @@
         <f aca="false">IF(O19="Y",T19,J19)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH19" s="16" t="n">
+      <c r="AH19" s="14" t="n">
+        <f aca="false">IF(OR(AF19="",Y19&lt;&gt;"Y"),"",INT(IF(O19="Y",V19,L19)/C19))</f>
+        <v>171444</v>
+      </c>
+      <c r="AI19" s="16" t="n">
         <f aca="false">AB19*IF(O19="Y",X19,N19)</f>
         <v>0.536</v>
       </c>
-      <c r="AI19" s="13"/>
-      <c r="AJ19" s="13" t="str">
+      <c r="AJ19" s="13"/>
+      <c r="AK19" s="13" t="str">
         <f aca="false">IF(AF19="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF19&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -3181,31 +3217,31 @@
         <v>13</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D20" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="F20" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="H20" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="I20" s="8" t="s">
-        <v>139</v>
-      </c>
       <c r="J20" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>4428400</v>
@@ -3220,7 +3256,7 @@
         <v>0.0135</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
@@ -3232,7 +3268,7 @@
       <c r="W20" s="8"/>
       <c r="X20" s="10"/>
       <c r="Y20" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z20" s="11" t="n">
         <v>0</v>
@@ -3265,14 +3301,18 @@
         <f aca="false">IF(O20="Y",T20,J20)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH20" s="12" t="n">
+      <c r="AH20" s="9" t="n">
+        <f aca="false">IF(OR(AF20="",Y20&lt;&gt;"Y"),"",INT(IF(O20="Y",V20,L20)/C20))</f>
+        <v>2651999</v>
+      </c>
+      <c r="AI20" s="12" t="n">
         <f aca="false">AB20*IF(O20="Y",X20,N20)</f>
         <v>0.675</v>
       </c>
-      <c r="AI20" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="AJ20" s="8" t="str">
+      <c r="AJ20" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK20" s="8" t="str">
         <f aca="false">IF(AF20="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF20&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -3282,31 +3322,31 @@
         <v>14</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D21" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="F21" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="13" t="s">
+      <c r="H21" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="I21" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="I21" s="13" t="s">
-        <v>146</v>
-      </c>
       <c r="J21" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K21" s="14" t="n">
         <v>254200</v>
@@ -3321,7 +3361,7 @@
         <v>0.0315</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
@@ -3333,7 +3373,7 @@
       <c r="W21" s="13"/>
       <c r="X21" s="15"/>
       <c r="Y21" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z21" s="11" t="n">
         <v>0</v>
@@ -3366,14 +3406,18 @@
         <f aca="false">IF(O21="Y",T21,J21)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH21" s="16" t="n">
+      <c r="AH21" s="14" t="n">
+        <f aca="false">IF(OR(AF21="",Y21&lt;&gt;"Y"),"",INT(IF(O21="Y",V21,L21)/C21))</f>
+        <v>84739</v>
+      </c>
+      <c r="AI21" s="16" t="n">
         <f aca="false">AB21*IF(O21="Y",X21,N21)</f>
         <v>0.63</v>
       </c>
-      <c r="AI21" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ21" s="13" t="str">
+      <c r="AJ21" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="AK21" s="13" t="str">
         <f aca="false">IF(AF21="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF21&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -3383,37 +3427,37 @@
         <v>15</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="F22" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="H22" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="H22" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>153</v>
-      </c>
       <c r="J22" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>890550</v>
+        <v>890450</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1205764</v>
+        <v>1205634</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>50</v>
@@ -3422,7 +3466,7 @@
         <v>0.0192</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
@@ -3434,7 +3478,7 @@
       <c r="W22" s="8"/>
       <c r="X22" s="10"/>
       <c r="Y22" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z22" s="11" t="n">
         <v>0</v>
@@ -3467,12 +3511,16 @@
         <f aca="false">IF(O22="Y",T22,J22)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH22" s="12" t="n">
+      <c r="AH22" s="9" t="n">
+        <f aca="false">IF(OR(AF22="",Y22&lt;&gt;"Y"),"",INT(IF(O22="Y",V22,L22)/C22))</f>
+        <v>1205634</v>
+      </c>
+      <c r="AI22" s="12" t="n">
         <f aca="false">AB22*IF(O22="Y",X22,N22)</f>
         <v>0.96</v>
       </c>
-      <c r="AI22" s="8"/>
-      <c r="AJ22" s="8" t="str">
+      <c r="AJ22" s="8"/>
+      <c r="AK22" s="8" t="str">
         <f aca="false">IF(AF22="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF22&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -3482,31 +3530,31 @@
         <v>16</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="F23" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="G23" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="H23" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="I23" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="I23" s="13" t="s">
-        <v>160</v>
-      </c>
       <c r="J23" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K23" s="14" t="n">
         <v>1475200</v>
@@ -3521,7 +3569,7 @@
         <v>0.0099</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
@@ -3533,7 +3581,7 @@
       <c r="W23" s="13"/>
       <c r="X23" s="15"/>
       <c r="Y23" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z23" s="11" t="n">
         <v>0</v>
@@ -3566,12 +3614,16 @@
         <f aca="false">IF(O23="Y",T23,J23)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH23" s="16" t="n">
+      <c r="AH23" s="14" t="n">
+        <f aca="false">IF(OR(AF23="",Y23&lt;&gt;"Y"),"",INT(IF(O23="Y",V23,L23)/C23))</f>
+        <v>746500</v>
+      </c>
+      <c r="AI23" s="16" t="n">
         <f aca="false">AB23*IF(O23="Y",X23,N23)</f>
         <v>0.99</v>
       </c>
-      <c r="AI23" s="13"/>
-      <c r="AJ23" s="13" t="str">
+      <c r="AJ23" s="13"/>
+      <c r="AK23" s="13" t="str">
         <f aca="false">IF(AF23="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF23&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -3581,31 +3633,31 @@
         <v>17</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="F24" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="G24" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="H24" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="I24" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>167</v>
-      </c>
       <c r="J24" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>0</v>
@@ -3620,7 +3672,7 @@
         <v>1.4914</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
@@ -3632,7 +3684,7 @@
       <c r="W24" s="8"/>
       <c r="X24" s="10"/>
       <c r="Y24" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z24" s="11" t="n">
         <v>0</v>
@@ -3665,14 +3717,18 @@
         <f aca="false">IF(O24="Y",T24,J24)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH24" s="12" t="n">
+      <c r="AH24" s="9" t="n">
+        <f aca="false">IF(OR(AF24="",Y24&lt;&gt;"Y"),"",INT(IF(O24="Y",V24,L24)/C24))</f>
+        <v>710</v>
+      </c>
+      <c r="AI24" s="12" t="n">
         <f aca="false">AB24*IF(O24="Y",X24,N24)</f>
         <v>1.4914</v>
       </c>
-      <c r="AI24" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="AJ24" s="8" t="str">
+      <c r="AJ24" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK24" s="8" t="str">
         <f aca="false">IF(AF24="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF24&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -3682,31 +3738,31 @@
         <v>18</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="F25" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="G25" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="H25" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="I25" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="I25" s="13" t="s">
-        <v>175</v>
-      </c>
       <c r="J25" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K25" s="14" t="n">
         <v>28050</v>
@@ -3721,7 +3777,7 @@
         <v>0.0764</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
@@ -3733,7 +3789,7 @@
       <c r="W25" s="13"/>
       <c r="X25" s="15"/>
       <c r="Y25" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z25" s="11" t="n">
         <v>0</v>
@@ -3766,14 +3822,18 @@
         <f aca="false">IF(O25="Y",T25,J25)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH25" s="16" t="n">
+      <c r="AH25" s="14" t="n">
+        <f aca="false">IF(OR(AF25="",Y25&lt;&gt;"Y"),"",INT(IF(O25="Y",V25,L25)/C25))</f>
+        <v>28059</v>
+      </c>
+      <c r="AI25" s="16" t="n">
         <f aca="false">AB25*IF(O25="Y",X25,N25)</f>
         <v>0.764</v>
       </c>
-      <c r="AI25" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="AJ25" s="13" t="str">
+      <c r="AJ25" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AK25" s="13" t="str">
         <f aca="false">IF(AF25="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF25&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -3783,31 +3843,31 @@
         <v>19</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="F26" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="G26" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="H26" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="I26" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>183</v>
-      </c>
       <c r="J26" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>933760</v>
@@ -3822,7 +3882,7 @@
         <v>0.0276</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
@@ -3834,7 +3894,7 @@
       <c r="W26" s="8"/>
       <c r="X26" s="10"/>
       <c r="Y26" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z26" s="11" t="n">
         <v>0</v>
@@ -3867,14 +3927,18 @@
         <f aca="false">IF(O26="Y",T26,J26)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH26" s="12" t="n">
+      <c r="AH26" s="9" t="n">
+        <f aca="false">IF(OR(AF26="",Y26&lt;&gt;"Y"),"",INT(IF(O26="Y",V26,L26)/C26))</f>
+        <v>1010306</v>
+      </c>
+      <c r="AI26" s="12" t="n">
         <f aca="false">AB26*IF(O26="Y",X26,N26)</f>
         <v>0.552</v>
       </c>
-      <c r="AI26" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="AJ26" s="8" t="str">
+      <c r="AJ26" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="AK26" s="8" t="str">
         <f aca="false">IF(AF26="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF26&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -3884,37 +3948,37 @@
         <v>20</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="F27" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="G27" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="H27" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="H27" s="13" t="s">
+      <c r="I27" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="I27" s="13" t="s">
-        <v>189</v>
-      </c>
       <c r="J27" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K27" s="14" t="n">
         <v>1151250</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>1161601</v>
+        <v>1161591</v>
       </c>
       <c r="M27" s="13" t="n">
         <v>50</v>
@@ -3923,7 +3987,7 @@
         <v>0.0184</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
@@ -3935,7 +3999,7 @@
       <c r="W27" s="13"/>
       <c r="X27" s="15"/>
       <c r="Y27" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z27" s="11" t="n">
         <v>0</v>
@@ -3968,14 +4032,18 @@
         <f aca="false">IF(O27="Y",T27,J27)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH27" s="16" t="n">
+      <c r="AH27" s="14" t="n">
+        <f aca="false">IF(OR(AF27="",Y27&lt;&gt;"Y"),"",INT(IF(O27="Y",V27,L27)/C27))</f>
+        <v>1161591</v>
+      </c>
+      <c r="AI27" s="16" t="n">
         <f aca="false">AB27*IF(O27="Y",X27,N27)</f>
         <v>0.92</v>
       </c>
-      <c r="AI27" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="AJ27" s="13" t="str">
+      <c r="AJ27" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="AK27" s="13" t="str">
         <f aca="false">IF(AF27="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF27&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -3985,19 +4053,19 @@
         <v>21</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="F28" s="8" t="s">
         <v>193</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>194</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
@@ -4008,7 +4076,7 @@
       <c r="M28" s="8"/>
       <c r="N28" s="10"/>
       <c r="O28" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
@@ -4020,7 +4088,7 @@
       <c r="W28" s="8"/>
       <c r="X28" s="10"/>
       <c r="Y28" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z28" s="11" t="n">
         <v>0</v>
@@ -4053,14 +4121,18 @@
         <f aca="false">IF(O28="Y",T28,J28)&amp;""</f>
         <v/>
       </c>
-      <c r="AH28" s="12" t="n">
+      <c r="AH28" s="9" t="str">
+        <f aca="false">IF(OR(AF28="",Y28&lt;&gt;"Y"),"",INT(IF(O28="Y",V28,L28)/C28))</f>
+        <v/>
+      </c>
+      <c r="AI28" s="12" t="n">
         <f aca="false">AB28*IF(O28="Y",X28,N28)</f>
         <v>0</v>
       </c>
-      <c r="AI28" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="AJ28" s="8" t="str">
+      <c r="AJ28" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="AK28" s="8" t="str">
         <f aca="false">IF(AF28="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF28&amp;".html","open"))</f>
         <v/>
       </c>
@@ -4070,31 +4142,31 @@
         <v>22</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="F29" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="G29" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="H29" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="I29" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>202</v>
-      </c>
       <c r="J29" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K29" s="14" t="n">
         <v>21230</v>
@@ -4109,7 +4181,7 @@
         <v>0.113</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
@@ -4121,7 +4193,7 @@
       <c r="W29" s="13"/>
       <c r="X29" s="15"/>
       <c r="Y29" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z29" s="11" t="n">
         <v>0</v>
@@ -4154,14 +4226,18 @@
         <f aca="false">IF(O29="Y",T29,J29)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH29" s="16" t="n">
+      <c r="AH29" s="14" t="n">
+        <f aca="false">IF(OR(AF29="",Y29&lt;&gt;"Y"),"",INT(IF(O29="Y",V29,L29)/C29))</f>
+        <v>21231</v>
+      </c>
+      <c r="AI29" s="16" t="n">
         <f aca="false">AB29*IF(O29="Y",X29,N29)</f>
         <v>0.565</v>
       </c>
-      <c r="AI29" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="AJ29" s="13" t="str">
+      <c r="AJ29" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="AK29" s="13" t="str">
         <f aca="false">IF(AF29="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF29&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -4171,31 +4247,31 @@
         <v>23</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D30" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="F30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="H30" s="8" t="s">
+      <c r="I30" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>208</v>
-      </c>
       <c r="J30" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>4980</v>
@@ -4210,7 +4286,7 @@
         <v>0.1242</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
@@ -4222,7 +4298,7 @@
       <c r="W30" s="8"/>
       <c r="X30" s="10"/>
       <c r="Y30" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z30" s="11" t="n">
         <v>0</v>
@@ -4255,14 +4331,18 @@
         <f aca="false">IF(O30="Y",T30,J30)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH30" s="12" t="n">
+      <c r="AH30" s="9" t="n">
+        <f aca="false">IF(OR(AF30="",Y30&lt;&gt;"Y"),"",INT(IF(O30="Y",V30,L30)/C30))</f>
+        <v>2490</v>
+      </c>
+      <c r="AI30" s="12" t="n">
         <f aca="false">AB30*IF(O30="Y",X30,N30)</f>
         <v>0.621</v>
       </c>
-      <c r="AI30" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ30" s="8" t="str">
+      <c r="AJ30" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="AK30" s="8" t="str">
         <f aca="false">IF(AF30="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF30&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -4272,37 +4352,37 @@
         <v>24</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="F31" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="G31" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="H31" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="I31" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="H31" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>215</v>
-      </c>
       <c r="J31" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K31" s="14" t="n">
         <v>681455</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>1074088</v>
+        <v>1074077</v>
       </c>
       <c r="M31" s="13" t="n">
         <v>5</v>
@@ -4311,7 +4391,7 @@
         <v>0.0853</v>
       </c>
       <c r="O31" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
@@ -4323,7 +4403,7 @@
       <c r="W31" s="13"/>
       <c r="X31" s="15"/>
       <c r="Y31" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z31" s="11" t="n">
         <v>0</v>
@@ -4356,12 +4436,16 @@
         <f aca="false">IF(O31="Y",T31,J31)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH31" s="16" t="n">
+      <c r="AH31" s="14" t="n">
+        <f aca="false">IF(OR(AF31="",Y31&lt;&gt;"Y"),"",INT(IF(O31="Y",V31,L31)/C31))</f>
+        <v>1074077</v>
+      </c>
+      <c r="AI31" s="16" t="n">
         <f aca="false">AB31*IF(O31="Y",X31,N31)</f>
         <v>0.4265</v>
       </c>
-      <c r="AI31" s="13"/>
-      <c r="AJ31" s="13" t="str">
+      <c r="AJ31" s="13"/>
+      <c r="AK31" s="13" t="str">
         <f aca="false">IF(AF31="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF31&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -4371,37 +4455,37 @@
         <v>25</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="F32" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="F32" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32" s="8" t="s">
+      <c r="H32" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="I32" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="I32" s="8" t="s">
-        <v>221</v>
-      </c>
       <c r="J32" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>2477700</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>3573902</v>
+        <v>3573872</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>100</v>
@@ -4410,7 +4494,7 @@
         <v>0.0056</v>
       </c>
       <c r="O32" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
@@ -4422,7 +4506,7 @@
       <c r="W32" s="8"/>
       <c r="X32" s="10"/>
       <c r="Y32" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z32" s="11" t="n">
         <v>0</v>
@@ -4455,12 +4539,16 @@
         <f aca="false">IF(O32="Y",T32,J32)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH32" s="12" t="n">
+      <c r="AH32" s="9" t="n">
+        <f aca="false">IF(OR(AF32="",Y32&lt;&gt;"Y"),"",INT(IF(O32="Y",V32,L32)/C32))</f>
+        <v>1786936</v>
+      </c>
+      <c r="AI32" s="12" t="n">
         <f aca="false">AB32*IF(O32="Y",X32,N32)</f>
         <v>0.56</v>
       </c>
-      <c r="AI32" s="8"/>
-      <c r="AJ32" s="8" t="str">
+      <c r="AJ32" s="8"/>
+      <c r="AK32" s="8" t="str">
         <f aca="false">IF(AF32="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF32&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -4470,31 +4558,31 @@
         <v>26</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>5</v>
       </c>
       <c r="D33" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="F33" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="H33" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="H33" s="13" t="s">
+      <c r="I33" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>226</v>
-      </c>
       <c r="J33" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K33" s="14" t="n">
         <v>2280000</v>
@@ -4509,7 +4597,7 @@
         <v>0.0049</v>
       </c>
       <c r="O33" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
@@ -4521,7 +4609,7 @@
       <c r="W33" s="13"/>
       <c r="X33" s="15"/>
       <c r="Y33" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z33" s="11" t="n">
         <v>0</v>
@@ -4554,12 +4642,16 @@
         <f aca="false">IF(O33="Y",T33,J33)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH33" s="16" t="n">
+      <c r="AH33" s="14" t="n">
+        <f aca="false">IF(OR(AF33="",Y33&lt;&gt;"Y"),"",INT(IF(O33="Y",V33,L33)/C33))</f>
+        <v>575997</v>
+      </c>
+      <c r="AI33" s="16" t="n">
         <f aca="false">AB33*IF(O33="Y",X33,N33)</f>
         <v>0.49</v>
       </c>
-      <c r="AI33" s="13"/>
-      <c r="AJ33" s="13" t="str">
+      <c r="AJ33" s="13"/>
+      <c r="AK33" s="13" t="str">
         <f aca="false">IF(AF33="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF33&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -4569,37 +4661,37 @@
         <v>27</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E34" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="F34" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="H34" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="F34" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="H34" s="8" t="s">
+      <c r="I34" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="I34" s="8" t="s">
-        <v>231</v>
-      </c>
       <c r="J34" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>27482800</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>31829431</v>
+        <v>31829451</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>100</v>
@@ -4608,22 +4700,22 @@
         <v>0.0041</v>
       </c>
       <c r="O34" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P34" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="R34" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="Q34" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="R34" s="8" t="s">
+      <c r="S34" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="S34" s="8" t="s">
-        <v>234</v>
-      </c>
       <c r="T34" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="U34" s="9" t="n">
         <v>4433300</v>
@@ -4638,7 +4730,7 @@
         <v>0.0039</v>
       </c>
       <c r="Y34" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z34" s="11" t="n">
         <v>0</v>
@@ -4671,14 +4763,18 @@
         <f aca="false">IF(O34="Y",T34,J34)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH34" s="12" t="n">
+      <c r="AH34" s="9" t="n">
+        <f aca="false">IF(OR(AF34="",Y34&lt;&gt;"Y"),"",INT(IF(O34="Y",V34,L34)/C34))</f>
+        <v>31829451</v>
+      </c>
+      <c r="AI34" s="12" t="n">
         <f aca="false">AB34*IF(O34="Y",X34,N34)</f>
         <v>0.41</v>
       </c>
-      <c r="AI34" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="AJ34" s="8" t="str">
+      <c r="AJ34" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="AK34" s="8" t="str">
         <f aca="false">IF(AF34="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF34&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -4688,37 +4784,37 @@
         <v>28</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>5</v>
       </c>
       <c r="D35" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="F35" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="H35" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="F35" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="H35" s="13" t="s">
+      <c r="I35" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="I35" s="13" t="s">
-        <v>240</v>
-      </c>
       <c r="J35" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K35" s="14" t="n">
         <v>44415400</v>
       </c>
       <c r="L35" s="14" t="n">
-        <v>51391042</v>
+        <v>51391005</v>
       </c>
       <c r="M35" s="13" t="n">
         <v>100</v>
@@ -4727,7 +4823,7 @@
         <v>0.0039</v>
       </c>
       <c r="O35" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
@@ -4739,7 +4835,7 @@
       <c r="W35" s="13"/>
       <c r="X35" s="15"/>
       <c r="Y35" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z35" s="11" t="n">
         <v>0</v>
@@ -4772,12 +4868,16 @@
         <f aca="false">IF(O35="Y",T35,J35)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH35" s="16" t="n">
+      <c r="AH35" s="14" t="n">
+        <f aca="false">IF(OR(AF35="",Y35&lt;&gt;"Y"),"",INT(IF(O35="Y",V35,L35)/C35))</f>
+        <v>10278201</v>
+      </c>
+      <c r="AI35" s="16" t="n">
         <f aca="false">AB35*IF(O35="Y",X35,N35)</f>
         <v>0.39</v>
       </c>
-      <c r="AI35" s="13"/>
-      <c r="AJ35" s="13" t="str">
+      <c r="AJ35" s="13"/>
+      <c r="AK35" s="13" t="str">
         <f aca="false">IF(AF35="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF35&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -4787,31 +4887,31 @@
         <v>29</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="F36" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="H36" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="F36" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="H36" s="8" t="s">
+      <c r="I36" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="I36" s="8" t="s">
-        <v>245</v>
-      </c>
       <c r="J36" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>445400</v>
@@ -4826,7 +4926,7 @@
         <v>0.0035</v>
       </c>
       <c r="O36" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
@@ -4838,7 +4938,7 @@
       <c r="W36" s="8"/>
       <c r="X36" s="10"/>
       <c r="Y36" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z36" s="11" t="n">
         <v>0</v>
@@ -4871,14 +4971,18 @@
         <f aca="false">IF(O36="Y",T36,J36)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH36" s="12" t="n">
+      <c r="AH36" s="9" t="n">
+        <f aca="false">IF(OR(AF36="",Y36&lt;&gt;"Y"),"",INT(IF(O36="Y",V36,L36)/C36))</f>
+        <v>832480</v>
+      </c>
+      <c r="AI36" s="12" t="n">
         <f aca="false">AB36*IF(O36="Y",X36,N36)</f>
         <v>0.35</v>
       </c>
-      <c r="AI36" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="AJ36" s="8" t="str">
+      <c r="AJ36" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="AK36" s="8" t="str">
         <f aca="false">IF(AF36="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF36&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -4888,31 +4992,31 @@
         <v>30</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D37" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="F37" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="H37" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="F37" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="H37" s="13" t="s">
+      <c r="I37" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="I37" s="13" t="s">
-        <v>251</v>
-      </c>
       <c r="J37" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K37" s="14" t="n">
         <v>76200</v>
@@ -4927,7 +5031,7 @@
         <v>0.003</v>
       </c>
       <c r="O37" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
@@ -4939,7 +5043,7 @@
       <c r="W37" s="13"/>
       <c r="X37" s="15"/>
       <c r="Y37" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z37" s="11" t="n">
         <v>0</v>
@@ -4972,12 +5076,16 @@
         <f aca="false">IF(O37="Y",T37,J37)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH37" s="16" t="n">
+      <c r="AH37" s="14" t="n">
+        <f aca="false">IF(OR(AF37="",Y37&lt;&gt;"Y"),"",INT(IF(O37="Y",V37,L37)/C37))</f>
+        <v>25701</v>
+      </c>
+      <c r="AI37" s="16" t="n">
         <f aca="false">AB37*IF(O37="Y",X37,N37)</f>
         <v>0.3</v>
       </c>
-      <c r="AI37" s="13"/>
-      <c r="AJ37" s="13" t="str">
+      <c r="AJ37" s="13"/>
+      <c r="AK37" s="13" t="str">
         <f aca="false">IF(AF37="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF37&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -4987,31 +5095,31 @@
         <v>31</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C38" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E38" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="F38" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="H38" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="F38" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="H38" s="8" t="s">
+      <c r="I38" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="I38" s="8" t="s">
-        <v>256</v>
-      </c>
       <c r="J38" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>29200</v>
@@ -5026,7 +5134,7 @@
         <v>0.0048</v>
       </c>
       <c r="O38" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
@@ -5038,7 +5146,7 @@
       <c r="W38" s="8"/>
       <c r="X38" s="10"/>
       <c r="Y38" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z38" s="11" t="n">
         <v>0</v>
@@ -5071,12 +5179,16 @@
         <f aca="false">IF(O38="Y",T38,J38)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH38" s="12" t="n">
+      <c r="AH38" s="9" t="n">
+        <f aca="false">IF(OR(AF38="",Y38&lt;&gt;"Y"),"",INT(IF(O38="Y",V38,L38)/C38))</f>
+        <v>29539</v>
+      </c>
+      <c r="AI38" s="12" t="n">
         <f aca="false">AB38*IF(O38="Y",X38,N38)</f>
         <v>0.48</v>
       </c>
-      <c r="AI38" s="8"/>
-      <c r="AJ38" s="8" t="str">
+      <c r="AJ38" s="8"/>
+      <c r="AK38" s="8" t="str">
         <f aca="false">IF(AF38="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF38&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -5086,31 +5198,31 @@
         <v>32</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D39" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="F39" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="H39" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="F39" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="H39" s="13" t="s">
+      <c r="I39" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="I39" s="13" t="s">
-        <v>261</v>
-      </c>
       <c r="J39" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K39" s="14" t="n">
         <v>5411400</v>
@@ -5125,7 +5237,7 @@
         <v>0.0045</v>
       </c>
       <c r="O39" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P39" s="13"/>
       <c r="Q39" s="13"/>
@@ -5137,7 +5249,7 @@
       <c r="W39" s="13"/>
       <c r="X39" s="15"/>
       <c r="Y39" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z39" s="11" t="n">
         <v>0</v>
@@ -5170,12 +5282,16 @@
         <f aca="false">IF(O39="Y",T39,J39)&amp;""</f>
         <v>Basic</v>
       </c>
-      <c r="AH39" s="16" t="n">
+      <c r="AH39" s="14" t="n">
+        <f aca="false">IF(OR(AF39="",Y39&lt;&gt;"Y"),"",INT(IF(O39="Y",V39,L39)/C39))</f>
+        <v>3551520</v>
+      </c>
+      <c r="AI39" s="16" t="n">
         <f aca="false">AB39*IF(O39="Y",X39,N39)</f>
         <v>0.45</v>
       </c>
-      <c r="AI39" s="13"/>
-      <c r="AJ39" s="13" t="str">
+      <c r="AJ39" s="13"/>
+      <c r="AK39" s="13" t="str">
         <f aca="false">IF(AF39="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF39&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -5185,31 +5301,31 @@
         <v>33</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D40" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="F40" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="G40" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="H40" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="I40" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="I40" s="8" t="s">
-        <v>268</v>
-      </c>
       <c r="J40" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>3520</v>
@@ -5224,7 +5340,7 @@
         <v>0.2615</v>
       </c>
       <c r="O40" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P40" s="8"/>
       <c r="Q40" s="8"/>
@@ -5236,7 +5352,7 @@
       <c r="W40" s="8"/>
       <c r="X40" s="10"/>
       <c r="Y40" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z40" s="11" t="n">
         <v>0</v>
@@ -5269,14 +5385,18 @@
         <f aca="false">IF(O40="Y",T40,J40)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH40" s="12" t="n">
+      <c r="AH40" s="9" t="n">
+        <f aca="false">IF(OR(AF40="",Y40&lt;&gt;"Y"),"",INT(IF(O40="Y",V40,L40)/C40))</f>
+        <v>1174</v>
+      </c>
+      <c r="AI40" s="12" t="n">
         <f aca="false">AB40*IF(O40="Y",X40,N40)</f>
         <v>1.3075</v>
       </c>
-      <c r="AI40" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="AJ40" s="8" t="str">
+      <c r="AJ40" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="AK40" s="8" t="str">
         <f aca="false">IF(AF40="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF40&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -5286,31 +5406,31 @@
         <v>34</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E41" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="F41" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="F41" s="13" t="s">
+      <c r="G41" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="H41" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="H41" s="13" t="s">
+      <c r="I41" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="I41" s="13" t="s">
-        <v>276</v>
-      </c>
       <c r="J41" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K41" s="14" t="n">
         <v>266</v>
@@ -5325,7 +5445,7 @@
         <v>0.6261</v>
       </c>
       <c r="O41" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P41" s="13"/>
       <c r="Q41" s="13"/>
@@ -5337,7 +5457,7 @@
       <c r="W41" s="13"/>
       <c r="X41" s="15"/>
       <c r="Y41" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z41" s="11" t="n">
         <v>0</v>
@@ -5370,14 +5490,18 @@
         <f aca="false">IF(O41="Y",T41,J41)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH41" s="16" t="n">
+      <c r="AH41" s="14" t="n">
+        <f aca="false">IF(OR(AF41="",Y41&lt;&gt;"Y"),"",INT(IF(O41="Y",V41,L41)/C41))</f>
+        <v>266</v>
+      </c>
+      <c r="AI41" s="16" t="n">
         <f aca="false">AB41*IF(O41="Y",X41,N41)</f>
         <v>0.6261</v>
       </c>
-      <c r="AI41" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="AJ41" s="13" t="str">
+      <c r="AJ41" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="AK41" s="13" t="str">
         <f aca="false">IF(AF41="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF41&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -5387,31 +5511,31 @@
         <v>35</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="F42" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="G42" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="H42" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="I42" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="H42" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="J42" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
@@ -5426,7 +5550,7 @@
         <v>7.5985</v>
       </c>
       <c r="O42" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
@@ -5438,7 +5562,7 @@
       <c r="W42" s="8"/>
       <c r="X42" s="10"/>
       <c r="Y42" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z42" s="11" t="n">
         <v>0</v>
@@ -5471,14 +5595,18 @@
         <f aca="false">IF(O42="Y",T42,J42)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH42" s="12" t="n">
+      <c r="AH42" s="9" t="n">
+        <f aca="false">IF(OR(AF42="",Y42&lt;&gt;"Y"),"",INT(IF(O42="Y",V42,L42)/C42))</f>
+        <v>0</v>
+      </c>
+      <c r="AI42" s="12" t="n">
         <f aca="false">AB42*IF(O42="Y",X42,N42)</f>
         <v>7.5985</v>
       </c>
-      <c r="AI42" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="AJ42" s="8" t="str">
+      <c r="AJ42" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="AK42" s="8" t="str">
         <f aca="false">IF(AF42="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF42&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -5488,31 +5616,31 @@
         <v>36</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="F43" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="G43" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="H43" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="H43" s="13" t="s">
+      <c r="I43" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="I43" s="13" t="s">
-        <v>291</v>
-      </c>
       <c r="J43" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K43" s="14" t="n">
         <v>208</v>
@@ -5527,7 +5655,7 @@
         <v>1.9017</v>
       </c>
       <c r="O43" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
@@ -5539,7 +5667,7 @@
       <c r="W43" s="13"/>
       <c r="X43" s="15"/>
       <c r="Y43" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z43" s="11" t="n">
         <v>0</v>
@@ -5572,14 +5700,18 @@
         <f aca="false">IF(O43="Y",T43,J43)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH43" s="16" t="n">
+      <c r="AH43" s="14" t="n">
+        <f aca="false">IF(OR(AF43="",Y43&lt;&gt;"Y"),"",INT(IF(O43="Y",V43,L43)/C43))</f>
+        <v>208</v>
+      </c>
+      <c r="AI43" s="16" t="n">
         <f aca="false">AB43*IF(O43="Y",X43,N43)</f>
         <v>1.9017</v>
       </c>
-      <c r="AI43" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="AJ43" s="13" t="str">
+      <c r="AJ43" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="AK43" s="13" t="str">
         <f aca="false">IF(AF43="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF43&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -5589,31 +5721,31 @@
         <v>37</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="E44" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="F44" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="G44" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="H44" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="I44" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="I44" s="8" t="s">
-        <v>299</v>
-      </c>
       <c r="J44" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>8793</v>
@@ -5628,7 +5760,7 @@
         <v>0.5665</v>
       </c>
       <c r="O44" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
@@ -5640,7 +5772,7 @@
       <c r="W44" s="8"/>
       <c r="X44" s="10"/>
       <c r="Y44" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z44" s="11" t="n">
         <v>0</v>
@@ -5673,12 +5805,16 @@
         <f aca="false">IF(O44="Y",T44,J44)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH44" s="12" t="n">
+      <c r="AH44" s="9" t="n">
+        <f aca="false">IF(OR(AF44="",Y44&lt;&gt;"Y"),"",INT(IF(O44="Y",V44,L44)/C44))</f>
+        <v>8793</v>
+      </c>
+      <c r="AI44" s="12" t="n">
         <f aca="false">AB44*IF(O44="Y",X44,N44)</f>
         <v>0.5665</v>
       </c>
-      <c r="AI44" s="8"/>
-      <c r="AJ44" s="8" t="str">
+      <c r="AJ44" s="8"/>
+      <c r="AK44" s="8" t="str">
         <f aca="false">IF(AF44="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF44&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -5688,31 +5824,31 @@
         <v>38</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="E45" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="F45" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="G45" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="H45" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="G45" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="H45" s="13" t="s">
+      <c r="I45" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="I45" s="13" t="s">
-        <v>305</v>
-      </c>
       <c r="J45" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K45" s="14" t="n">
         <v>100</v>
@@ -5727,22 +5863,22 @@
         <v>5.4546</v>
       </c>
       <c r="O45" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P45" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q45" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="R45" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="Q45" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="R45" s="13" t="s">
+      <c r="S45" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="S45" s="13" t="s">
-        <v>308</v>
-      </c>
       <c r="T45" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U45" s="14" t="n">
         <v>180</v>
@@ -5757,7 +5893,7 @@
         <v>4.8285</v>
       </c>
       <c r="Y45" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z45" s="11" t="n">
         <v>0</v>
@@ -5790,14 +5926,18 @@
         <f aca="false">IF(O45="Y",T45,J45)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH45" s="16" t="n">
+      <c r="AH45" s="14" t="n">
+        <f aca="false">IF(OR(AF45="",Y45&lt;&gt;"Y"),"",INT(IF(O45="Y",V45,L45)/C45))</f>
+        <v>100</v>
+      </c>
+      <c r="AI45" s="16" t="n">
         <f aca="false">AB45*IF(O45="Y",X45,N45)</f>
         <v>5.4546</v>
       </c>
-      <c r="AI45" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="AJ45" s="13" t="str">
+      <c r="AJ45" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="AK45" s="13" t="str">
         <f aca="false">IF(AF45="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF45&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -5807,37 +5947,37 @@
         <v>39</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="E46" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="F46" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="G46" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="I46" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="G46" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>314</v>
-      </c>
       <c r="J46" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>43755</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>45743</v>
+        <v>45736</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>5</v>
@@ -5846,7 +5986,7 @@
         <v>0.1778</v>
       </c>
       <c r="O46" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P46" s="8"/>
       <c r="Q46" s="8"/>
@@ -5858,7 +5998,7 @@
       <c r="W46" s="8"/>
       <c r="X46" s="10"/>
       <c r="Y46" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z46" s="11" t="n">
         <v>0</v>
@@ -5891,14 +6031,18 @@
         <f aca="false">IF(O46="Y",T46,J46)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH46" s="12" t="n">
+      <c r="AH46" s="9" t="n">
+        <f aca="false">IF(OR(AF46="",Y46&lt;&gt;"Y"),"",INT(IF(O46="Y",V46,L46)/C46))</f>
+        <v>45736</v>
+      </c>
+      <c r="AI46" s="12" t="n">
         <f aca="false">AB46*IF(O46="Y",X46,N46)</f>
         <v>0.889</v>
       </c>
-      <c r="AI46" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="AJ46" s="8" t="str">
+      <c r="AJ46" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="AK46" s="8" t="str">
         <f aca="false">IF(AF46="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF46&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -5908,31 +6052,31 @@
         <v>40</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="E47" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="F47" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="F47" s="13" t="s">
+      <c r="G47" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="G47" s="13" t="s">
+      <c r="H47" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="H47" s="13" t="s">
+      <c r="I47" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="I47" s="13" t="s">
-        <v>322</v>
-      </c>
       <c r="J47" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K47" s="14" t="n">
         <v>6440</v>
@@ -5947,7 +6091,7 @@
         <v>0.1106</v>
       </c>
       <c r="O47" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P47" s="13"/>
       <c r="Q47" s="13"/>
@@ -5959,7 +6103,7 @@
       <c r="W47" s="13"/>
       <c r="X47" s="15"/>
       <c r="Y47" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z47" s="11" t="n">
         <v>0</v>
@@ -5992,14 +6136,18 @@
         <f aca="false">IF(O47="Y",T47,J47)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH47" s="16" t="n">
+      <c r="AH47" s="14" t="n">
+        <f aca="false">IF(OR(AF47="",Y47&lt;&gt;"Y"),"",INT(IF(O47="Y",V47,L47)/C47))</f>
+        <v>9243</v>
+      </c>
+      <c r="AI47" s="16" t="n">
         <f aca="false">AB47*IF(O47="Y",X47,N47)</f>
         <v>0.553</v>
       </c>
-      <c r="AI47" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="AJ47" s="13" t="str">
+      <c r="AJ47" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="AK47" s="13" t="str">
         <f aca="false">IF(AF47="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF47&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -6009,31 +6157,31 @@
         <v>41</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="F48" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="G48" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="H48" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="H48" s="8" t="s">
+      <c r="I48" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="I48" s="8" t="s">
-        <v>330</v>
-      </c>
       <c r="J48" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>129910</v>
@@ -6048,7 +6196,7 @@
         <v>0.2032</v>
       </c>
       <c r="O48" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P48" s="8"/>
       <c r="Q48" s="8"/>
@@ -6060,7 +6208,7 @@
       <c r="W48" s="8"/>
       <c r="X48" s="10"/>
       <c r="Y48" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z48" s="11" t="n">
         <v>0</v>
@@ -6093,14 +6241,18 @@
         <f aca="false">IF(O48="Y",T48,J48)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH48" s="12" t="n">
+      <c r="AH48" s="9" t="n">
+        <f aca="false">IF(OR(AF48="",Y48&lt;&gt;"Y"),"",INT(IF(O48="Y",V48,L48)/C48))</f>
+        <v>136924</v>
+      </c>
+      <c r="AI48" s="12" t="n">
         <f aca="false">AB48*IF(O48="Y",X48,N48)</f>
         <v>1.016</v>
       </c>
-      <c r="AI48" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="AJ48" s="8" t="str">
+      <c r="AJ48" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="AK48" s="8" t="str">
         <f aca="false">IF(AF48="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF48&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -6110,19 +6262,19 @@
         <v>42</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E49" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="E49" s="13" t="s">
+      <c r="F49" s="13" t="s">
         <v>334</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>335</v>
       </c>
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
@@ -6133,7 +6285,7 @@
       <c r="M49" s="13"/>
       <c r="N49" s="15"/>
       <c r="O49" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P49" s="13"/>
       <c r="Q49" s="13"/>
@@ -6145,7 +6297,7 @@
       <c r="W49" s="13"/>
       <c r="X49" s="15"/>
       <c r="Y49" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z49" s="11" t="n">
         <v>0</v>
@@ -6178,14 +6330,18 @@
         <f aca="false">IF(O49="Y",T49,J49)&amp;""</f>
         <v/>
       </c>
-      <c r="AH49" s="16" t="n">
+      <c r="AH49" s="14" t="str">
+        <f aca="false">IF(OR(AF49="",Y49&lt;&gt;"Y"),"",INT(IF(O49="Y",V49,L49)/C49))</f>
+        <v/>
+      </c>
+      <c r="AI49" s="16" t="n">
         <f aca="false">AB49*IF(O49="Y",X49,N49)</f>
         <v>0</v>
       </c>
-      <c r="AI49" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="AJ49" s="13" t="str">
+      <c r="AJ49" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="AK49" s="13" t="str">
         <f aca="false">IF(AF49="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF49&amp;".html","open"))</f>
         <v/>
       </c>
@@ -6195,29 +6351,29 @@
         <v>43</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D50" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="E50" s="8" t="s">
         <v>338</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>339</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>48240</v>
@@ -6232,7 +6388,7 @@
         <v>0.0358</v>
       </c>
       <c r="O50" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
@@ -6244,7 +6400,7 @@
       <c r="W50" s="8"/>
       <c r="X50" s="10"/>
       <c r="Y50" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z50" s="11" t="n">
         <v>0</v>
@@ -6277,14 +6433,18 @@
         <f aca="false">IF(O50="Y",T50,J50)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH50" s="12" t="n">
+      <c r="AH50" s="9" t="str">
+        <f aca="false">IF(OR(AF50="",Y50&lt;&gt;"Y"),"",INT(IF(O50="Y",V50,L50)/C50))</f>
+        <v/>
+      </c>
+      <c r="AI50" s="12" t="n">
         <f aca="false">AB50*IF(O50="Y",X50,N50)</f>
         <v>0</v>
       </c>
-      <c r="AI50" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="AJ50" s="8" t="str">
+      <c r="AJ50" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="AK50" s="8" t="str">
         <f aca="false">IF(AF50="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF50&amp;".html","open"))</f>
         <v>open</v>
       </c>
@@ -6294,29 +6454,29 @@
         <v>44</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D51" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>343</v>
       </c>
       <c r="F51" s="13"/>
       <c r="G51" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K51" s="14" t="n">
         <v>328100</v>
@@ -6331,7 +6491,7 @@
         <v>0.0129</v>
       </c>
       <c r="O51" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P51" s="13"/>
       <c r="Q51" s="13"/>
@@ -6343,7 +6503,7 @@
       <c r="W51" s="13"/>
       <c r="X51" s="15"/>
       <c r="Y51" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z51" s="11" t="n">
         <v>0</v>
@@ -6376,59 +6536,63 @@
         <f aca="false">IF(O51="Y",T51,J51)&amp;""</f>
         <v>Extended</v>
       </c>
-      <c r="AH51" s="16" t="n">
+      <c r="AH51" s="14" t="str">
+        <f aca="false">IF(OR(AF51="",Y51&lt;&gt;"Y"),"",INT(IF(O51="Y",V51,L51)/C51))</f>
+        <v/>
+      </c>
+      <c r="AI51" s="16" t="n">
         <f aca="false">AB51*IF(O51="Y",X51,N51)</f>
         <v>0</v>
       </c>
-      <c r="AI51" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="AJ51" s="13" t="str">
+      <c r="AJ51" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="AK51" s="13" t="str">
         <f aca="false">IF(AF51="","",HYPERLINK("https://www.lcsc.com/product-detail/"&amp;AF51&amp;".html","open"))</f>
         <v>open</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AF53" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI53" s="17" t="n">
+        <f aca="false">SUM(AI8:AI51)</f>
+        <v>40.7078</v>
+      </c>
+      <c r="AJ53" s="18" t="s">
         <v>346</v>
-      </c>
-      <c r="AH53" s="17" t="n">
-        <f aca="false">SUM(AH8:AH51)</f>
-        <v>40.7078</v>
-      </c>
-      <c r="AI53" s="18" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AF54" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="AH54" s="20" t="n">
+        <v>347</v>
+      </c>
+      <c r="AI54" s="20" t="n">
         <f aca="false">COUNTIF(AB8:AB51,"&gt;0")</f>
         <v>40</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AF55" s="19" t="s">
-        <v>349</v>
-      </c>
-      <c r="AH55" s="20" t="n">
+        <v>348</v>
+      </c>
+      <c r="AI55" s="20" t="n">
         <f aca="false">COUNTIFS(AG8:AG51,"Extended",AB8:AB51,"&gt;0")</f>
         <v>24</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AF56" s="19" t="s">
-        <v>350</v>
-      </c>
-      <c r="AH56" s="20" t="n">
+        <v>349</v>
+      </c>
+      <c r="AI56" s="20" t="n">
         <f aca="false">COUNTIFS(AG8:AG51,"Basic",AB8:AB51,"&gt;0")+COUNTIFS(AG8:AG51,"Preferred ext.",AB8:AB51,"&gt;0")</f>
         <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:AJ51"/>
+  <autoFilter ref="A7:AK51"/>
   <conditionalFormatting sqref="K8:K51">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>AND($O8&lt;&gt;"Y",$Y8="Y",K8&lt;$AB8)</formula>
@@ -6447,6 +6611,11 @@
   <conditionalFormatting sqref="V8:V51">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>AND($O8="Y",$Y8="Y",V8&lt;$AA8)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH8:AH51">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(ISNUMBER(AH8),AH8&lt;$B$4)</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6475,16 +6644,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>351</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="C1" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="21" t="s">
         <v>352</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7234,19 +7403,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>354</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="C1" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="D1" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="21" t="s">
         <v>356</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
